--- a/insurance_data/ICICI_Lombard_Integrated_Model.xlsx
+++ b/insurance_data/ICICI_Lombard_Integrated_Model.xlsx
@@ -13,6 +13,7 @@
     <sheet name="D_Competitors" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="E_LTV_Detail" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="F_Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="G_Source_Screenshots" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,8 +76,31 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00996600"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -107,6 +131,12 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6DCE4"/>
+        <bgColor rgb="00D6DCE4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -120,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -145,6 +175,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -219,6 +255,261 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="7400925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="7400925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="7400925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>177</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="7400925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>231</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="7400925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>285</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="7400925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>339</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="7400925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>400</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="6772275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>450</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="6772275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>500</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="6772275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2145,7 +2436,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="7" t="inlineStr">
         <is>
           <t>D2C OPPORTUNITY (SOM)</t>
@@ -2832,10 +3122,10 @@
   <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A38:C38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5422,4 +5712,345 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H563"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE DOCUMENT SCREENSHOTS - AUDIT TRAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Screenshots extracted from official PDF reports | Use for McKinsey deck verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>📄 CBDT ITR Statistics AY 2023-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Source URL:</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>https://incometaxindia.gov.in/Documents/Direct%20Tax%20Data/Approved-version-Income-Tax-Return-Statistics-for-the-AY-2023-24.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Data Extracted:</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Total ITR Filers: 7.97 Cr | Income slab distribution | Salaried taxpayers: 3.80 Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Pages Used:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6, 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Page 6 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
+        <is>
+          <t>Page 9 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="inlineStr">
+        <is>
+          <t>Page 10 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="18" t="inlineStr">
+        <is>
+          <t>📄 Niva Bupa DRHP Industry Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>Source URL:</t>
+        </is>
+      </c>
+      <c r="B174" s="19" t="inlineStr">
+        <is>
+          <t>https://transactions.nivabupa.com/pages/doc/drhp/Industry-Report.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="13" t="inlineStr">
+        <is>
+          <t>Data Extracted:</t>
+        </is>
+      </c>
+      <c r="B175" s="20" t="inlineStr">
+        <is>
+          <t>Health insurance market size | Retail 38.7%, Group 50.5% | SAHI growth 27.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="inlineStr">
+        <is>
+          <t>Pages Used:</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1, 12, 15, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="21" t="inlineStr">
+        <is>
+          <t>Page 1 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="21" t="inlineStr">
+        <is>
+          <t>Page 12 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="21" t="inlineStr">
+        <is>
+          <t>Page 15 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="21" t="inlineStr">
+        <is>
+          <t>Page 18 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="18" t="inlineStr">
+        <is>
+          <t>📄 Niva Bupa Annual Report FY24</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="13" t="inlineStr">
+        <is>
+          <t>Source URL:</t>
+        </is>
+      </c>
+      <c r="B397" s="19" t="inlineStr">
+        <is>
+          <t>https://transactions.nivabupa.com/pages/doc/pub-dis/annual-reports/Annual-Report-FY-2023-24.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="13" t="inlineStr">
+        <is>
+          <t>Data Extracted:</t>
+        </is>
+      </c>
+      <c r="B398" s="20" t="inlineStr">
+        <is>
+          <t>GWP Rs 5,499 Cr | Claims ratio | Distribution mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="13" t="inlineStr">
+        <is>
+          <t>Pages Used:</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>1, 10, 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="21" t="inlineStr">
+        <is>
+          <t>Page 1 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="21" t="inlineStr">
+        <is>
+          <t>Page 10 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="21" t="inlineStr">
+        <is>
+          <t>Page 45 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="18" t="inlineStr">
+        <is>
+          <t>📄 IRDAI Annual Report 2023-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="13" t="inlineStr">
+        <is>
+          <t>Source URL:</t>
+        </is>
+      </c>
+      <c r="B554" s="19" t="inlineStr">
+        <is>
+          <t>https://irdai.gov.in/documents/37343/418498/IRDAI+Annual+Report+2023-24.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="13" t="inlineStr">
+        <is>
+          <t>Data Extracted:</t>
+        </is>
+      </c>
+      <c r="B555" s="20" t="inlineStr">
+        <is>
+          <t>Total Premium Rs 11.19T | Penetration 3.7% | Claims Ratios</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="13" t="inlineStr">
+        <is>
+          <t>Pages Used:</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>1, 45, 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Page 1:</t>
+        </is>
+      </c>
+      <c r="B557" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Page 45:</t>
+        </is>
+      </c>
+      <c r="B558" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Page 52:</t>
+        </is>
+      </c>
+      <c r="B559" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="23" t="inlineStr">
+        <is>
+          <t>NOTE: Some government PDFs have download restrictions. Screenshots shown where available.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B555:H555"/>
+    <mergeCell ref="B397:H397"/>
+    <mergeCell ref="B554:H554"/>
+    <mergeCell ref="B175:H175"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A553:H553"/>
+    <mergeCell ref="A563:H563"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B398:H398"/>
+    <mergeCell ref="A396:H396"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A173:H173"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B174:H174"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/insurance_data/ICICI_Lombard_Integrated_Model.xlsx
+++ b/insurance_data/ICICI_Lombard_Integrated_Model.xlsx
@@ -338,7 +338,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>177</row>
+      <row>188</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5238750" cy="7400925"/>
@@ -363,7 +363,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>231</row>
+      <row>242</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5238750" cy="7400925"/>
@@ -388,7 +388,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>285</row>
+      <row>296</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5238750" cy="7400925"/>
@@ -413,7 +413,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>339</row>
+      <row>350</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5238750" cy="7400925"/>
@@ -438,10 +438,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>400</row>
+      <row>404</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5238750" cy="6772275"/>
+    <ext cx="5238750" cy="7400925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -463,10 +463,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>450</row>
+      <row>458</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5238750" cy="6772275"/>
+    <ext cx="5238750" cy="7400925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -488,7 +488,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>500</row>
+      <row>519</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5238750" cy="6772275"/>
@@ -499,6 +499,81 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>569</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="6772275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>619</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="6772275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>669</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5238750" cy="6772275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5720,7 +5795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H563"/>
+  <dimension ref="A1:H742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5814,7 +5889,7 @@
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>📄 Niva Bupa DRHP Industry Report</t>
+          <t>📄 GI Council Yearbook 2023-24</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5901,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>https://transactions.nivabupa.com/pages/doc/drhp/Industry-Report.pdf</t>
+          <t>https://www.gicouncil.in/yearbook/2023-24/wp-content/uploads/GIC_Yearbook_2023-24.pdf</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5913,7 @@
       </c>
       <c r="B175" s="20" t="inlineStr">
         <is>
-          <t>Health insurance market size | Retail 38.7%, Group 50.5% | SAHI growth 27.1%</t>
+          <t>GDPI Rs 2,89,673 Cr | Health &amp; PA 40.3% | Motor 31.7% | Growth 12.4%</t>
         </is>
       </c>
     </row>
@@ -5850,205 +5925,402 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1, 12, 15, 18</t>
+          <t>1, 8, 12, 15</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="21" t="inlineStr">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Page 1:</t>
+        </is>
+      </c>
+      <c r="B177" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Page 8:</t>
+        </is>
+      </c>
+      <c r="B178" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Page 12:</t>
+        </is>
+      </c>
+      <c r="B179" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Page 15:</t>
+        </is>
+      </c>
+      <c r="B180" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
+        <is>
+          <t>📄 Niva Bupa DRHP Industry Report (Redseer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="13" t="inlineStr">
+        <is>
+          <t>Source URL:</t>
+        </is>
+      </c>
+      <c r="B185" s="19" t="inlineStr">
+        <is>
+          <t>https://transactions.nivabupa.com/pages/doc/drhp/Industry-Report.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="13" t="inlineStr">
+        <is>
+          <t>Data Extracted:</t>
+        </is>
+      </c>
+      <c r="B186" s="20" t="inlineStr">
+        <is>
+          <t>Health GWP Rs 1.08T | Retail 38.7% | Group 50.5% | SAHI 27.1% growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="13" t="inlineStr">
+        <is>
+          <t>Pages Used:</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5, 9, 12, 15, 17, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="21" t="inlineStr">
+        <is>
+          <t>Page 5 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="21" t="inlineStr">
+        <is>
+          <t>Page 9 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="21" t="inlineStr">
+        <is>
+          <t>Page 12 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="21" t="inlineStr">
+        <is>
+          <t>Page 15 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="21" t="inlineStr">
+        <is>
+          <t>Page 17 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="21" t="inlineStr">
+        <is>
+          <t>Page 20 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="18" t="inlineStr">
+        <is>
+          <t>📄 Niva Bupa Annual Report FY24</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="13" t="inlineStr">
+        <is>
+          <t>Source URL:</t>
+        </is>
+      </c>
+      <c r="B516" s="19" t="inlineStr">
+        <is>
+          <t>https://transactions.nivabupa.com/pages/doc/pub-dis/annual-reports/Annual-Report-FY-2023-24.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="13" t="inlineStr">
+        <is>
+          <t>Data Extracted:</t>
+        </is>
+      </c>
+      <c r="B517" s="20" t="inlineStr">
+        <is>
+          <t>GWP Rs 5,499 Cr | 41% Growth | CSR 100% | Distribution mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="13" t="inlineStr">
+        <is>
+          <t>Pages Used:</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>1, 8, 12, 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="21" t="inlineStr">
         <is>
           <t>Page 1 Screenshot:</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="21" t="inlineStr">
+    <row r="569">
+      <c r="A569" s="21" t="inlineStr">
+        <is>
+          <t>Page 8 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="21" t="inlineStr">
         <is>
           <t>Page 12 Screenshot:</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="21" t="inlineStr">
-        <is>
-          <t>Page 15 Screenshot:</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="21" t="inlineStr">
-        <is>
-          <t>Page 18 Screenshot:</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="18" t="inlineStr">
-        <is>
-          <t>📄 Niva Bupa Annual Report FY24</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="13" t="inlineStr">
+    <row r="669">
+      <c r="A669" s="21" t="inlineStr">
+        <is>
+          <t>Page 45 Screenshot:</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="18" t="inlineStr">
+        <is>
+          <t>📄 Star Health Annual Report FY24</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="13" t="inlineStr">
         <is>
           <t>Source URL:</t>
         </is>
       </c>
-      <c r="B397" s="19" t="inlineStr">
-        <is>
-          <t>https://transactions.nivabupa.com/pages/doc/pub-dis/annual-reports/Annual-Report-FY-2023-24.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="13" t="inlineStr">
+      <c r="B723" s="19" t="inlineStr">
+        <is>
+          <t>https://www.starhealth.in/sites/default/files/Star-Health-Annual-Report-2023-24.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="13" t="inlineStr">
         <is>
           <t>Data Extracted:</t>
         </is>
       </c>
-      <c r="B398" s="20" t="inlineStr">
-        <is>
-          <t>GWP Rs 5,499 Cr | Claims ratio | Distribution mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="13" t="inlineStr">
+      <c r="B724" s="20" t="inlineStr">
+        <is>
+          <t>GWP Rs 15,254 Cr | Claims Ratio 66.5% | 7L+ Agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="13" t="inlineStr">
         <is>
           <t>Pages Used:</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>1, 10, 45</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="21" t="inlineStr">
-        <is>
-          <t>Page 1 Screenshot:</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" s="21" t="inlineStr">
-        <is>
-          <t>Page 10 Screenshot:</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" s="21" t="inlineStr">
-        <is>
-          <t>Page 45 Screenshot:</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" s="18" t="inlineStr">
-        <is>
-          <t>📄 IRDAI Annual Report 2023-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" s="13" t="inlineStr">
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>1, 10, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Page 1:</t>
+        </is>
+      </c>
+      <c r="B726" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Page 10:</t>
+        </is>
+      </c>
+      <c r="B727" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Page 25:</t>
+        </is>
+      </c>
+      <c r="B728" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="18" t="inlineStr">
+        <is>
+          <t>📄 ICICI Lombard Annual Report FY24</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="13" t="inlineStr">
         <is>
           <t>Source URL:</t>
         </is>
       </c>
-      <c r="B554" s="19" t="inlineStr">
-        <is>
-          <t>https://irdai.gov.in/documents/37343/418498/IRDAI+Annual+Report+2023-24.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" s="13" t="inlineStr">
+      <c r="B733" s="19" t="inlineStr">
+        <is>
+          <t>https://www.icicilombard.com/docs/default-source/financial-information/annualreport2024.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="13" t="inlineStr">
         <is>
           <t>Data Extracted:</t>
         </is>
       </c>
-      <c r="B555" s="20" t="inlineStr">
-        <is>
-          <t>Total Premium Rs 11.19T | Penetration 3.7% | Claims Ratios</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" s="13" t="inlineStr">
+      <c r="B734" s="20" t="inlineStr">
+        <is>
+          <t>GDPI Rs 24,776 Cr | Market Share 8.67% | Solvency 2.69x</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="13" t="inlineStr">
         <is>
           <t>Pages Used:</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>1, 45, 52</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>1, 15, 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
         <is>
           <t>Page 1:</t>
         </is>
       </c>
-      <c r="B557" s="22" t="inlineStr">
+      <c r="B736" s="22" t="inlineStr">
         <is>
           <t>[Screenshot pending - see URL above for source]</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Page 15:</t>
+        </is>
+      </c>
+      <c r="B737" s="22" t="inlineStr">
+        <is>
+          <t>[Screenshot pending - see URL above for source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
         <is>
           <t>Page 45:</t>
         </is>
       </c>
-      <c r="B558" s="22" t="inlineStr">
+      <c r="B738" s="22" t="inlineStr">
         <is>
           <t>[Screenshot pending - see URL above for source]</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>Page 52:</t>
-        </is>
-      </c>
-      <c r="B559" s="22" t="inlineStr">
-        <is>
-          <t>[Screenshot pending - see URL above for source]</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" s="23" t="inlineStr">
+    <row r="742">
+      <c r="A742" s="23" t="inlineStr">
         <is>
           <t>NOTE: Some government PDFs have download restrictions. Screenshots shown where available.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="21">
+    <mergeCell ref="A742:H742"/>
+    <mergeCell ref="A732:H732"/>
+    <mergeCell ref="B733:H733"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A722:H722"/>
+    <mergeCell ref="B723:H723"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B516:H516"/>
+    <mergeCell ref="B185:H185"/>
+    <mergeCell ref="B734:H734"/>
+    <mergeCell ref="B724:H724"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A515:H515"/>
+    <mergeCell ref="B517:H517"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B555:H555"/>
-    <mergeCell ref="B397:H397"/>
-    <mergeCell ref="B554:H554"/>
+    <mergeCell ref="A184:H184"/>
     <mergeCell ref="B175:H175"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A553:H553"/>
-    <mergeCell ref="A563:H563"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B398:H398"/>
-    <mergeCell ref="A396:H396"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A173:H173"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="B174:H174"/>
+    <mergeCell ref="B186:H186"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
